--- a/ir_derivatives/input/irs_input.xlsx
+++ b/ir_derivatives/input/irs_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\ir_derivatives\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B74F32-C6BC-4885-9CA6-60CF1E6D3172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50EEB3D-5D74-4174-8000-8FB2374FED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="57">
   <si>
     <t>report_date</t>
   </si>
@@ -180,6 +180,30 @@
   </si>
   <si>
     <t>IRS_014</t>
+  </si>
+  <si>
+    <t>IRS_015</t>
+  </si>
+  <si>
+    <t>IRS_016</t>
+  </si>
+  <si>
+    <t>IRS_017</t>
+  </si>
+  <si>
+    <t>IRS_018</t>
+  </si>
+  <si>
+    <t>IRS_019</t>
+  </si>
+  <si>
+    <t>IRS_020</t>
+  </si>
+  <si>
+    <t>IRS_021</t>
+  </si>
+  <si>
+    <t>IRS_022</t>
   </si>
 </sst>
 </file>
@@ -550,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
@@ -639,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>80000000</v>
+        <v>50000000</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -701,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2">
-        <v>80000000</v>
+        <v>50000000</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
@@ -763,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>95000000</v>
+        <v>50000000</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
@@ -825,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="F5" t="s">
         <v>22</v>
@@ -887,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>100000000</v>
+        <v>50000000</v>
       </c>
       <c r="F6" t="s">
         <v>22</v>
@@ -1073,16 +1097,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="3">
-        <v>45488</v>
+        <v>45092</v>
       </c>
       <c r="H9" s="3">
-        <v>46583</v>
+        <v>46188</v>
       </c>
       <c r="I9">
         <v>4.4999999999999998E-2</v>
@@ -1097,13 +1121,13 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N9" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O9" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1135,16 +1159,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="3">
-        <v>45519</v>
+        <v>45122</v>
       </c>
       <c r="H10" s="3">
-        <v>46614</v>
+        <v>46218</v>
       </c>
       <c r="I10">
         <v>4.4999999999999998E-2</v>
@@ -1159,13 +1183,13 @@
         <v>27</v>
       </c>
       <c r="M10" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N10" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O10" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1197,16 +1221,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="3">
-        <v>45550</v>
+        <v>45153</v>
       </c>
       <c r="H11" s="3">
-        <v>46645</v>
+        <v>46249</v>
       </c>
       <c r="I11">
         <v>4.4999999999999998E-2</v>
@@ -1221,13 +1245,13 @@
         <v>27</v>
       </c>
       <c r="M11" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N11" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O11" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -1259,16 +1283,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="2">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
       </c>
-      <c r="G12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" t="s">
-        <v>24</v>
+      <c r="G12" s="3">
+        <v>45184</v>
+      </c>
+      <c r="H12" s="3">
+        <v>46280</v>
       </c>
       <c r="I12">
         <v>4.4999999999999998E-2</v>
@@ -1283,13 +1307,13 @@
         <v>27</v>
       </c>
       <c r="M12" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N12" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O12" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -1321,16 +1345,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="2">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13" s="3">
-        <v>45611</v>
+        <v>45214</v>
       </c>
       <c r="H13" s="3">
-        <v>46706</v>
+        <v>46310</v>
       </c>
       <c r="I13">
         <v>4.4999999999999998E-2</v>
@@ -1345,13 +1369,13 @@
         <v>27</v>
       </c>
       <c r="M13" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N13" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O13" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -1383,16 +1407,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>150000000</v>
+        <v>100000000</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14" s="3">
-        <v>45641</v>
+        <v>45245</v>
       </c>
       <c r="H14" s="3">
-        <v>46736</v>
+        <v>46341</v>
       </c>
       <c r="I14">
         <v>4.4999999999999998E-2</v>
@@ -1407,13 +1431,13 @@
         <v>27</v>
       </c>
       <c r="M14" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N14" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O14" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -1445,51 +1469,547 @@
         <v>0</v>
       </c>
       <c r="E15" s="2">
+        <v>100000000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="3">
+        <v>45275</v>
+      </c>
+      <c r="H15" s="3">
+        <v>46371</v>
+      </c>
+      <c r="I15">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" t="s">
+        <v>28</v>
+      </c>
+      <c r="O15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>29</v>
+      </c>
+      <c r="R15" t="s">
+        <v>27</v>
+      </c>
+      <c r="S15" t="s">
+        <v>31</v>
+      </c>
+      <c r="T15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>100000000</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3">
+        <v>45306</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46402</v>
+      </c>
+      <c r="I16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" t="s">
+        <v>27</v>
+      </c>
+      <c r="S16" t="s">
+        <v>31</v>
+      </c>
+      <c r="T16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
         <v>150000000</v>
       </c>
-      <c r="F15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="3">
+        <v>45458</v>
+      </c>
+      <c r="H17" s="3">
+        <v>46553</v>
+      </c>
+      <c r="I17">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N17" t="s">
+        <v>44</v>
+      </c>
+      <c r="O17" t="s">
+        <v>44</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>29</v>
+      </c>
+      <c r="R17" t="s">
+        <v>27</v>
+      </c>
+      <c r="S17" t="s">
+        <v>31</v>
+      </c>
+      <c r="T17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="3">
+        <v>45488</v>
+      </c>
+      <c r="H18" s="3">
+        <v>46583</v>
+      </c>
+      <c r="I18">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" t="s">
+        <v>43</v>
+      </c>
+      <c r="N18" t="s">
+        <v>44</v>
+      </c>
+      <c r="O18" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>29</v>
+      </c>
+      <c r="R18" t="s">
+        <v>27</v>
+      </c>
+      <c r="S18" t="s">
+        <v>31</v>
+      </c>
+      <c r="T18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="3">
+        <v>45519</v>
+      </c>
+      <c r="H19" s="3">
+        <v>46614</v>
+      </c>
+      <c r="I19">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N19" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>29</v>
+      </c>
+      <c r="R19" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" t="s">
+        <v>31</v>
+      </c>
+      <c r="T19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3">
+        <v>45550</v>
+      </c>
+      <c r="H20" s="3">
+        <v>46645</v>
+      </c>
+      <c r="I20">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>25</v>
+      </c>
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" t="s">
+        <v>44</v>
+      </c>
+      <c r="O20" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>29</v>
+      </c>
+      <c r="R20" t="s">
+        <v>27</v>
+      </c>
+      <c r="S20" t="s">
+        <v>31</v>
+      </c>
+      <c r="T20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>29</v>
+      </c>
+      <c r="R21" t="s">
+        <v>27</v>
+      </c>
+      <c r="S21" t="s">
+        <v>31</v>
+      </c>
+      <c r="T21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="3">
+        <v>45611</v>
+      </c>
+      <c r="H22" s="3">
+        <v>46706</v>
+      </c>
+      <c r="I22">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" t="s">
+        <v>44</v>
+      </c>
+      <c r="O22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>29</v>
+      </c>
+      <c r="R22" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" t="s">
+        <v>31</v>
+      </c>
+      <c r="T22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="F23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="3">
         <v>45641</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H23" s="3">
         <v>46736</v>
       </c>
-      <c r="I15">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J15" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" t="s">
+      <c r="I23">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="s">
         <v>43</v>
       </c>
-      <c r="N15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" t="s">
-        <v>27</v>
-      </c>
-      <c r="S15" t="s">
-        <v>31</v>
-      </c>
-      <c r="T15" t="s">
+      <c r="N23" t="s">
+        <v>44</v>
+      </c>
+      <c r="O23" t="s">
+        <v>44</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>29</v>
+      </c>
+      <c r="R23" t="s">
+        <v>27</v>
+      </c>
+      <c r="S23" t="s">
+        <v>31</v>
+      </c>
+      <c r="T23" t="s">
         <v>32</v>
       </c>
     </row>

--- a/ir_derivatives/input/irs_input.xlsx
+++ b/ir_derivatives/input/irs_input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\ir_derivatives\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50EEB3D-5D74-4174-8000-8FB2374FED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3764C2-1F96-4D12-AF55-7462254DC0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F11" t="s">
         <v>22</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F12" t="s">
         <v>22</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>100000000</v>
+        <v>90000000</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="2">
-        <v>150000000</v>
+        <v>90000000</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="2">
-        <v>150000000</v>
+        <v>120000000</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="2">
-        <v>150000000</v>
+        <v>120000000</v>
       </c>
       <c r="F19" t="s">
         <v>22</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>150000000</v>
+        <v>120000000</v>
       </c>
       <c r="F20" t="s">
         <v>22</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>150000000</v>
+        <v>120000000</v>
       </c>
       <c r="F21" t="s">
         <v>22</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>150000000</v>
+        <v>120000000</v>
       </c>
       <c r="F22" t="s">
         <v>22</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="2">
-        <v>150000000</v>
+        <v>120000000</v>
       </c>
       <c r="F23" t="s">
         <v>22</v>

--- a/ir_derivatives/input/irs_input.xlsx
+++ b/ir_derivatives/input/irs_input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzimi\Documents\data_engineering\data_projects\git_hub_projects\bank_project\ir_derivatives\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3764C2-1F96-4D12-AF55-7462254DC0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BABE48-6CD1-43B0-8D59-52D5AAF67E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="44">
   <si>
     <t>report_date</t>
   </si>
@@ -161,49 +161,10 @@
     <t>IRS_009</t>
   </si>
   <si>
-    <t>IRS_010</t>
-  </si>
-  <si>
     <t>PLN_ASK_6M</t>
   </si>
   <si>
     <t>6M</t>
-  </si>
-  <si>
-    <t>IRS_011</t>
-  </si>
-  <si>
-    <t>IRS_012</t>
-  </si>
-  <si>
-    <t>IRS_013</t>
-  </si>
-  <si>
-    <t>IRS_014</t>
-  </si>
-  <si>
-    <t>IRS_015</t>
-  </si>
-  <si>
-    <t>IRS_016</t>
-  </si>
-  <si>
-    <t>IRS_017</t>
-  </si>
-  <si>
-    <t>IRS_018</t>
-  </si>
-  <si>
-    <t>IRS_019</t>
-  </si>
-  <si>
-    <t>IRS_020</t>
-  </si>
-  <si>
-    <t>IRS_021</t>
-  </si>
-  <si>
-    <t>IRS_022</t>
   </si>
 </sst>
 </file>
@@ -574,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
@@ -663,16 +624,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
       </c>
       <c r="G2" s="3">
-        <v>44576</v>
+        <v>45275</v>
       </c>
       <c r="H2" s="3">
-        <v>45672</v>
+        <v>46371</v>
       </c>
       <c r="I2">
         <v>4.4999999999999998E-2</v>
@@ -725,16 +686,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="2">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="F3" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="3">
-        <v>44757</v>
+        <v>45306</v>
       </c>
       <c r="H3" s="3">
-        <v>45853</v>
+        <v>46402</v>
       </c>
       <c r="I3">
         <v>4.4999999999999998E-2</v>
@@ -749,13 +710,13 @@
         <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="N3" t="s">
         <v>28</v>
       </c>
       <c r="O3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -787,16 +748,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="3">
-        <v>44819</v>
+        <v>45458</v>
       </c>
       <c r="H4" s="3">
-        <v>45915</v>
+        <v>46553</v>
       </c>
       <c r="I4">
         <v>4.4999999999999998E-2</v>
@@ -811,13 +772,13 @@
         <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -855,10 +816,10 @@
         <v>22</v>
       </c>
       <c r="G5" s="3">
-        <v>44972</v>
+        <v>45488</v>
       </c>
       <c r="H5" s="3">
-        <v>46068</v>
+        <v>46583</v>
       </c>
       <c r="I5">
         <v>4.4999999999999998E-2</v>
@@ -873,13 +834,13 @@
         <v>27</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -917,10 +878,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="3">
-        <v>45000</v>
+        <v>45519</v>
       </c>
       <c r="H6" s="3">
-        <v>46096</v>
+        <v>46614</v>
       </c>
       <c r="I6">
         <v>4.4999999999999998E-2</v>
@@ -935,13 +896,13 @@
         <v>27</v>
       </c>
       <c r="M6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -973,16 +934,16 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>90000000</v>
+        <v>50000000</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="3">
-        <v>45031</v>
+        <v>45550</v>
       </c>
       <c r="H7" s="3">
-        <v>46127</v>
+        <v>46645</v>
       </c>
       <c r="I7">
         <v>4.4999999999999998E-2</v>
@@ -997,13 +958,13 @@
         <v>27</v>
       </c>
       <c r="M7" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="P7">
         <v>0</v>
@@ -1035,16 +996,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>90000000</v>
+        <v>50000000</v>
       </c>
       <c r="F8" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="3">
-        <v>45061</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46157</v>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
       </c>
       <c r="I8">
         <v>4.4999999999999998E-2</v>
@@ -1059,13 +1020,13 @@
         <v>27</v>
       </c>
       <c r="M8" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O8" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1097,16 +1058,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <v>90000000</v>
+        <v>50000000</v>
       </c>
       <c r="F9" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="3">
-        <v>45092</v>
+        <v>45611</v>
       </c>
       <c r="H9" s="3">
-        <v>46188</v>
+        <v>46706</v>
       </c>
       <c r="I9">
         <v>4.4999999999999998E-2</v>
@@ -1121,13 +1082,13 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O9" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -1159,16 +1120,16 @@
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>90000000</v>
+        <v>50000000</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="3">
-        <v>45122</v>
+        <v>45641</v>
       </c>
       <c r="H10" s="3">
-        <v>46218</v>
+        <v>46736</v>
       </c>
       <c r="I10">
         <v>4.4999999999999998E-2</v>
@@ -1183,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="M10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N10" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="O10" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -1204,812 +1165,6 @@
         <v>31</v>
       </c>
       <c r="T10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="F11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3">
-        <v>45153</v>
-      </c>
-      <c r="H11" s="3">
-        <v>46249</v>
-      </c>
-      <c r="I11">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O11" t="s">
-        <v>28</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" t="s">
-        <v>27</v>
-      </c>
-      <c r="S11" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="F12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3">
-        <v>45184</v>
-      </c>
-      <c r="H12" s="3">
-        <v>46280</v>
-      </c>
-      <c r="I12">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" t="s">
-        <v>30</v>
-      </c>
-      <c r="N12" t="s">
-        <v>28</v>
-      </c>
-      <c r="O12" t="s">
-        <v>28</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>29</v>
-      </c>
-      <c r="R12" t="s">
-        <v>27</v>
-      </c>
-      <c r="S12" t="s">
-        <v>31</v>
-      </c>
-      <c r="T12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="F13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3">
-        <v>45214</v>
-      </c>
-      <c r="H13" s="3">
-        <v>46310</v>
-      </c>
-      <c r="I13">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J13" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" t="s">
-        <v>30</v>
-      </c>
-      <c r="N13" t="s">
-        <v>28</v>
-      </c>
-      <c r="O13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" t="s">
-        <v>27</v>
-      </c>
-      <c r="S13" t="s">
-        <v>31</v>
-      </c>
-      <c r="T13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="F14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3">
-        <v>45245</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46341</v>
-      </c>
-      <c r="I14">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J14" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" t="s">
-        <v>30</v>
-      </c>
-      <c r="N14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>29</v>
-      </c>
-      <c r="R14" t="s">
-        <v>27</v>
-      </c>
-      <c r="S14" t="s">
-        <v>31</v>
-      </c>
-      <c r="T14" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="F15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3">
-        <v>45275</v>
-      </c>
-      <c r="H15" s="3">
-        <v>46371</v>
-      </c>
-      <c r="I15">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J15" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" t="s">
-        <v>30</v>
-      </c>
-      <c r="N15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" t="s">
-        <v>28</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" t="s">
-        <v>27</v>
-      </c>
-      <c r="S15" t="s">
-        <v>31</v>
-      </c>
-      <c r="T15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3">
-        <v>45306</v>
-      </c>
-      <c r="H16" s="3">
-        <v>46402</v>
-      </c>
-      <c r="I16">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J16" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" t="s">
-        <v>28</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>29</v>
-      </c>
-      <c r="R16" t="s">
-        <v>27</v>
-      </c>
-      <c r="S16" t="s">
-        <v>31</v>
-      </c>
-      <c r="T16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>90000000</v>
-      </c>
-      <c r="F17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3">
-        <v>45458</v>
-      </c>
-      <c r="H17" s="3">
-        <v>46553</v>
-      </c>
-      <c r="I17">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J17" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" t="s">
-        <v>43</v>
-      </c>
-      <c r="N17" t="s">
-        <v>44</v>
-      </c>
-      <c r="O17" t="s">
-        <v>44</v>
-      </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>29</v>
-      </c>
-      <c r="R17" t="s">
-        <v>27</v>
-      </c>
-      <c r="S17" t="s">
-        <v>31</v>
-      </c>
-      <c r="T17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <v>120000000</v>
-      </c>
-      <c r="F18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3">
-        <v>45488</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46583</v>
-      </c>
-      <c r="I18">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J18" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" t="s">
-        <v>43</v>
-      </c>
-      <c r="N18" t="s">
-        <v>44</v>
-      </c>
-      <c r="O18" t="s">
-        <v>44</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>29</v>
-      </c>
-      <c r="R18" t="s">
-        <v>27</v>
-      </c>
-      <c r="S18" t="s">
-        <v>31</v>
-      </c>
-      <c r="T18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2">
-        <v>120000000</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="3">
-        <v>45519</v>
-      </c>
-      <c r="H19" s="3">
-        <v>46614</v>
-      </c>
-      <c r="I19">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J19" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" t="s">
-        <v>27</v>
-      </c>
-      <c r="M19" t="s">
-        <v>43</v>
-      </c>
-      <c r="N19" t="s">
-        <v>44</v>
-      </c>
-      <c r="O19" t="s">
-        <v>44</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>29</v>
-      </c>
-      <c r="R19" t="s">
-        <v>27</v>
-      </c>
-      <c r="S19" t="s">
-        <v>31</v>
-      </c>
-      <c r="T19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2">
-        <v>120000000</v>
-      </c>
-      <c r="F20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3">
-        <v>45550</v>
-      </c>
-      <c r="H20" s="3">
-        <v>46645</v>
-      </c>
-      <c r="I20">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J20" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M20" t="s">
-        <v>43</v>
-      </c>
-      <c r="N20" t="s">
-        <v>44</v>
-      </c>
-      <c r="O20" t="s">
-        <v>44</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>29</v>
-      </c>
-      <c r="R20" t="s">
-        <v>27</v>
-      </c>
-      <c r="S20" t="s">
-        <v>31</v>
-      </c>
-      <c r="T20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2">
-        <v>120000000</v>
-      </c>
-      <c r="F21" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21" t="s">
-        <v>23</v>
-      </c>
-      <c r="H21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I21">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J21" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N21" t="s">
-        <v>44</v>
-      </c>
-      <c r="O21" t="s">
-        <v>44</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>29</v>
-      </c>
-      <c r="R21" t="s">
-        <v>27</v>
-      </c>
-      <c r="S21" t="s">
-        <v>31</v>
-      </c>
-      <c r="T21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2">
-        <v>120000000</v>
-      </c>
-      <c r="F22" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3">
-        <v>45611</v>
-      </c>
-      <c r="H22" s="3">
-        <v>46706</v>
-      </c>
-      <c r="I22">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J22" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" t="s">
-        <v>27</v>
-      </c>
-      <c r="M22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N22" t="s">
-        <v>44</v>
-      </c>
-      <c r="O22" t="s">
-        <v>44</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>29</v>
-      </c>
-      <c r="R22" t="s">
-        <v>27</v>
-      </c>
-      <c r="S22" t="s">
-        <v>31</v>
-      </c>
-      <c r="T22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2">
-        <v>120000000</v>
-      </c>
-      <c r="F23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="3">
-        <v>45641</v>
-      </c>
-      <c r="H23" s="3">
-        <v>46736</v>
-      </c>
-      <c r="I23">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J23" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" t="s">
-        <v>43</v>
-      </c>
-      <c r="N23" t="s">
-        <v>44</v>
-      </c>
-      <c r="O23" t="s">
-        <v>44</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>29</v>
-      </c>
-      <c r="R23" t="s">
-        <v>27</v>
-      </c>
-      <c r="S23" t="s">
-        <v>31</v>
-      </c>
-      <c r="T23" t="s">
         <v>32</v>
       </c>
     </row>

--- a/ir_derivatives/input/irs_input.xlsx
+++ b/ir_derivatives/input/irs_input.xlsx
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45275</v>
+        <v>45821</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46371</v>
+        <v>46917</v>
       </c>
       <c r="I2" t="n">
         <v>0.045</v>
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45306</v>
+        <v>45852</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46402</v>
+        <v>46948</v>
       </c>
       <c r="I3" t="n">
         <v>0.045</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45458</v>
+        <v>46004</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46553</v>
+        <v>47099</v>
       </c>
       <c r="I4" t="n">
         <v>0.045</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45488</v>
+        <v>46034</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46583</v>
+        <v>47129</v>
       </c>
       <c r="I5" t="n">
         <v>0.045</v>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45519</v>
+        <v>46065</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46614</v>
+        <v>47160</v>
       </c>
       <c r="I6" t="n">
         <v>0.045</v>
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45550</v>
+        <v>46096</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46645</v>
+        <v>47191</v>
       </c>
       <c r="I7" t="n">
         <v>0.045</v>
@@ -1075,15 +1075,11 @@
           <t>PLN</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2027-10-15</t>
-        </is>
+      <c r="G8" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>47221</v>
       </c>
       <c r="I8" t="n">
         <v>0.045</v>
@@ -1168,10 +1164,10 @@
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45611</v>
+        <v>46157</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46706</v>
+        <v>47252</v>
       </c>
       <c r="I9" t="n">
         <v>0.045</v>
@@ -1256,10 +1252,10 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45641</v>
+        <v>46187</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46736</v>
+        <v>47282</v>
       </c>
       <c r="I10" t="n">
         <v>0.045</v>

--- a/ir_derivatives/input/irs_input.xlsx
+++ b/ir_derivatives/input/irs_input.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,8 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +525,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -547,10 +549,10 @@
           <t>PLN</t>
         </is>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="3" t="n">
         <v>45821</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="3" t="n">
         <v>46917</v>
       </c>
       <c r="I2" t="n">
@@ -611,7 +613,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -635,10 +637,10 @@
           <t>PLN</t>
         </is>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="3" t="n">
         <v>45852</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="3" t="n">
         <v>46948</v>
       </c>
       <c r="I3" t="n">
@@ -699,7 +701,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -723,11 +725,11 @@
           <t>PLN</t>
         </is>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>46004</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>47099</v>
+      <c r="G4" s="3" t="n">
+        <v>45915</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>47011</v>
       </c>
       <c r="I4" t="n">
         <v>0.045</v>
@@ -787,7 +789,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -804,18 +806,18 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>PLN</t>
         </is>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>46034</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>47129</v>
+      <c r="G5" s="3" t="n">
+        <v>45945</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>47041</v>
       </c>
       <c r="I5" t="n">
         <v>0.045</v>
@@ -875,7 +877,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -892,18 +894,18 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>PLN</t>
         </is>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>46065</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>47160</v>
+      <c r="G6" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>47071</v>
       </c>
       <c r="I6" t="n">
         <v>0.045</v>
@@ -963,7 +965,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -980,18 +982,18 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>PLN</t>
         </is>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>46096</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>47191</v>
+      <c r="G7" s="3" t="n">
+        <v>46004</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>47099</v>
       </c>
       <c r="I7" t="n">
         <v>0.045</v>
@@ -1051,7 +1053,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1075,11 +1077,11 @@
           <t>PLN</t>
         </is>
       </c>
-      <c r="G8" s="1" t="n">
-        <v>46126</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>47221</v>
+      <c r="G8" s="3" t="n">
+        <v>46034</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>47129</v>
       </c>
       <c r="I8" t="n">
         <v>0.045</v>
@@ -1139,7 +1141,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1163,11 +1165,11 @@
           <t>PLN</t>
         </is>
       </c>
-      <c r="G9" s="1" t="n">
-        <v>46157</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>47252</v>
+      <c r="G9" s="3" t="n">
+        <v>46065</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>47160</v>
       </c>
       <c r="I9" t="n">
         <v>0.045</v>
@@ -1227,7 +1229,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1251,11 +1253,11 @@
           <t>PLN</t>
         </is>
       </c>
-      <c r="G10" s="1" t="n">
-        <v>46187</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>47282</v>
+      <c r="G10" s="3" t="n">
+        <v>46096</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>47191</v>
       </c>
       <c r="I10" t="n">
         <v>0.045</v>
@@ -1309,6 +1311,270 @@
         </is>
       </c>
       <c r="T10" t="inlineStr">
+        <is>
+          <t>PLN_fwd_curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IRS_010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IRS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>46126</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>47221</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ACT/ACT</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ModifiedFollowing</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>PLN_ASK_6M</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ACT/365</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ModifiedFollowing</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>PLN_disc_curve</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>PLN_fwd_curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IRS_011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>IRS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>46157</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ACT/ACT</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ModifiedFollowing</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>PLN_ASK_6M</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ACT/365</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ModifiedFollowing</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>PLN_disc_curve</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>PLN_fwd_curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IRS_012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IRS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>46187</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>47282</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ACT/ACT</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ModifiedFollowing</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>PLN_ASK_6M</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ACT/365</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>ModifiedFollowing</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>PLN_disc_curve</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>PLN_fwd_curve</t>
         </is>
